--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_49_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_49_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8277</v>
+        <v>4.5257</v>
       </c>
       <c r="E2" t="n">
-        <v>4.082</v>
+        <v>4.7465</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2544</v>
+        <v>-0.2208</v>
       </c>
       <c r="G2" t="n">
         <v>1.6871</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0038</v>
+        <v>-0.3058</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6642</v>
+        <v>0.0002</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3396</v>
+        <v>-0.306</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3053</v>
+        <v>1.3897</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1584</v>
+        <v>2.2764</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8531</v>
+        <v>-0.8867</v>
       </c>
       <c r="G3" t="n">
         <v>1.6632</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4274</v>
+        <v>-0.3431</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.286</v>
+        <v>-0.3196</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4681</v>
+        <v>0.2225</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5453</v>
+        <v>1.2661</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0772</v>
+        <v>-1.0436</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5647</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.127</v>
+        <v>-0.3725</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5623</v>
+        <v>0.2831</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6893</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2571</v>
+        <v>-0.2334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8873</v>
+        <v>1.1841</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1444</v>
+        <v>-1.4174</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5136</v>
+        <v>-2.247</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4129</v>
+        <v>-0.0888</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1008</v>
+        <v>-2.1582</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5548</v>
+        <v>0.216</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1211</v>
+        <v>1.9494</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.7334</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9588</v>
+        <v>-2.463</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.534</v>
+        <v>-2.0382</v>
       </c>
       <c r="O5" t="n">
         <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9524</v>
+        <v>-0.2752</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7616</v>
+        <v>0.3029</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8092</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.829</v>
+        <v>-0.4253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6225000000000001</v>
+        <v>-0.8499</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4515</v>
+        <v>0.4246</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0505</v>
+        <v>-2.9366</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1573</v>
+        <v>0.3158</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2078</v>
+        <v>-3.2524</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2868</v>
+        <v>-0.8815</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1763</v>
+        <v>1.21</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>-2.0915</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3373</v>
+        <v>-2.0551</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0191</v>
+        <v>-0.8942</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3182</v>
+        <v>-1.1609</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8298</v>
+        <v>-0.4345</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4955</v>
+        <v>0.0316</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3343</v>
+        <v>-0.4661</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.039</v>
+        <v>-0.8357</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3964</v>
+        <v>-1.4553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3574</v>
+        <v>0.6196</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9366</v>
+        <v>-1.5653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3158</v>
+        <v>-1.3612</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2524</v>
+        <v>-0.2041</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8815</v>
+        <v>-0.9932</v>
       </c>
       <c r="K7" t="n">
-        <v>1.21</v>
+        <v>-0.6351</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0915</v>
+        <v>-0.3581</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0551</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8942</v>
+        <v>-0.7261</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1609</v>
+        <v>0.154</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0482</v>
+        <v>-0.5023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5149</v>
+        <v>0.0198</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5333</v>
+        <v>-0.5221</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.074</v>
+        <v>-0.8497</v>
       </c>
       <c r="E8" t="n">
-        <v>0.209</v>
+        <v>0.093</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.283</v>
+        <v>-0.9427</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.247</v>
+        <v>-2.5136</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0888</v>
+        <v>-1.4129</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1582</v>
+        <v>-1.1008</v>
       </c>
       <c r="J8" t="n">
-        <v>0.216</v>
+        <v>-0.5548</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9494</v>
+        <v>0.1211</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7334</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.463</v>
+        <v>-1.9588</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0382</v>
+        <v>-1.534</v>
       </c>
       <c r="O8" t="n">
         <v>-0.4248</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1158</v>
+        <v>0.3598</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.9673</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4437</v>
+        <v>-0.6075</v>
       </c>
       <c r="V8" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1052</v>
+        <v>-1.1466</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6912</v>
+        <v>-0.0362</v>
       </c>
       <c r="F9" t="n">
-        <v>0.586</v>
+        <v>-1.1104</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5653</v>
+        <v>-1.0945</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3612</v>
+        <v>0.1836</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2041</v>
+        <v>-1.2781</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9932</v>
+        <v>0.632</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6351</v>
+        <v>1.3815</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3581</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-1.7265</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7261</v>
+        <v>-1.1979</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>-0.5286</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7718</v>
+        <v>0.4118</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2161</v>
+        <v>0.7235</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5557</v>
+        <v>-0.3117</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4983</v>
+        <v>-1.536</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4215</v>
+        <v>0.1507</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0768</v>
+        <v>-1.6868</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0945</v>
+        <v>-1.0505</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1836</v>
+        <v>0.1573</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2781</v>
+        <v>-1.2078</v>
       </c>
       <c r="J10" t="n">
-        <v>0.632</v>
+        <v>1.2868</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3815</v>
+        <v>1.1763</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7265</v>
+        <v>-2.3373</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1979</v>
+        <v>-1.0191</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5286</v>
+        <v>-1.3182</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0602</v>
+        <v>0.1228</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>0.0237</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2781</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1771</v>
+        <v>-1.9509</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1165</v>
+        <v>-1.9239</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0606</v>
+        <v>-0.027</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1223</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3589</v>
+        <v>-0.1327</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.0314</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6532</v>
+        <v>-2.4366</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3474</v>
+        <v>-0.198</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3058</v>
+        <v>-2.2386</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4868</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4859</v>
+        <v>-0.2693</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4129</v>
+        <v>0.5623</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8988</v>
+        <v>-0.8316</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1917</v>
+        <v>-3.8269</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0631</v>
+        <v>-1.6647</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1286</v>
+        <v>-2.1623</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9557</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7639</v>
+        <v>0.1287</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5375</v>
+        <v>0.9359</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7736</v>
+        <v>-0.8072</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.2235</v>
+        <v>-7.103200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.468399999999999</v>
+        <v>3.588799999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.692</v>
+        <v>-10.6921</v>
       </c>
       <c r="G14" t="n">
         <v>-12.1867</v>
@@ -1546,16 +1546,16 @@
         <v>19.7161</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.732499999999999</v>
+        <v>-1.6123</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6753</v>
+        <v>3.7954</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.4079</v>
+        <v>-5.4078</v>
       </c>
       <c r="V14" t="n">
-        <v>3.2166</v>
+        <v>3.216600000000001</v>
       </c>
       <c r="W14" t="n">
         <v>9.933399999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7154</v>
+        <v>6.2489</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9595</v>
+        <v>5.5022</v>
       </c>
       <c r="F15" t="n">
-        <v>1.756</v>
+        <v>0.7466</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1851</v>
+        <v>3.4612</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2413</v>
+        <v>1.9792</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4264</v>
+        <v>1.482</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0219</v>
+        <v>4.3726</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4823</v>
+        <v>2.8841</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5395</v>
+        <v>1.4885</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8368</v>
+        <v>-0.9115</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7236</v>
+        <v>-0.9049</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8868</v>
+        <v>-0.0065</v>
       </c>
       <c r="P15" t="n">
         <v>-0.4639</v>
@@ -1624,28 +1624,28 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4582</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1849</v>
+        <v>0.5546</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2733</v>
+        <v>0.0165</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>3.3584</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3338</v>
+        <v>5.2187</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9125</v>
+        <v>4.6714</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4213</v>
+        <v>0.5473</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4612</v>
+        <v>5.2885</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9792</v>
+        <v>1.3469</v>
       </c>
       <c r="I16" t="n">
-        <v>1.482</v>
+        <v>3.9415</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3726</v>
+        <v>5.3277</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8841</v>
+        <v>1.7477</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4885</v>
+        <v>3.58</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9115</v>
+        <v>-0.0393</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9049</v>
+        <v>-0.4008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0065</v>
+        <v>0.3615</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.344</v>
+        <v>0.0747</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>0.5034</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3088</v>
+        <v>-0.4288</v>
       </c>
       <c r="V16" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7926</v>
+        <v>4.8181</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6714</v>
+        <v>3.3081</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1212</v>
+        <v>1.51</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2885</v>
+        <v>3.1851</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3469</v>
+        <v>-0.2413</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9415</v>
+        <v>3.4264</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3277</v>
+        <v>4.0219</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7477</v>
+        <v>1.4823</v>
       </c>
       <c r="L17" t="n">
-        <v>3.58</v>
+        <v>2.5395</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0393</v>
+        <v>-0.8368</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4008</v>
+        <v>-1.7236</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3615</v>
+        <v>0.8868</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.7834</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3514</v>
+        <v>1.5608</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5034</v>
+        <v>1.5336</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8549</v>
+        <v>0.0272</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8628</v>
+        <v>3.0548</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6035</v>
+        <v>2.1896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2593</v>
+        <v>0.8652</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7168</v>
+        <v>1.679</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5594</v>
+        <v>0.3038</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1574</v>
+        <v>1.3752</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5639</v>
+        <v>2.2191</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4535</v>
+        <v>1.6805</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>0.5386</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8472</v>
+        <v>-0.5401</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8942</v>
+        <v>-1.3767</v>
       </c>
       <c r="O18" t="n">
-        <v>0.047</v>
+        <v>0.8366</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4501</v>
+        <v>0.1592</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1993</v>
+        <v>0.3776</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2508</v>
+        <v>-0.2183</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4993</v>
+        <v>1.6395</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8358</v>
+        <v>1.6599</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6635</v>
+        <v>-0.0203</v>
       </c>
       <c r="G19" t="n">
-        <v>1.679</v>
+        <v>1.7168</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3038</v>
+        <v>1.5594</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3752</v>
+        <v>0.1574</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2191</v>
+        <v>2.5639</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6805</v>
+        <v>2.4535</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5386</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5401</v>
+        <v>-0.8472</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3767</v>
+        <v>-0.8942</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8366</v>
+        <v>0.047</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3962</v>
+        <v>0.2269</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0237</v>
+        <v>0.2557</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.42</v>
+        <v>-0.0288</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1444</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2795</v>
+        <v>0.9529</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8242</v>
+        <v>1.296</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5448</v>
+        <v>-0.3431</v>
       </c>
       <c r="G20" t="n">
         <v>0.9774</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0174</v>
+        <v>-0.344</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3576</v>
+        <v>0.1142</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4582</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0085</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6193</v>
+        <v>0.3918</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6278</v>
+        <v>-1.0174</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7471</v>
+        <v>-0.205</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2017</v>
+        <v>-0.6601</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5454</v>
+        <v>0.4551</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.3563</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-0.0134</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1357</v>
+        <v>-0.5613</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3361</v>
+        <v>-1.0299</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4718</v>
+        <v>0.4685</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3888</v>
+        <v>0.1878</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2399</v>
+        <v>0.2675</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1489</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0967</v>
+        <v>-1.1094</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1559</v>
+        <v>0.6193</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2526</v>
+        <v>-1.7286</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.205</v>
+        <v>0.7471</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6601</v>
+        <v>0.2017</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4551</v>
+        <v>0.5454</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3563</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3697</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0134</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5613</v>
+        <v>0.1357</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0299</v>
+        <v>-0.3361</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4685</v>
+        <v>0.4718</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.232</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2834</v>
+        <v>0.288</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0316</v>
+        <v>0.2399</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.315</v>
+        <v>0.0481</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2188</v>
+        <v>-1.2632</v>
       </c>
       <c r="E23" t="n">
         <v>-1.7715</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5527</v>
+        <v>0.5083</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4502</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5535</v>
+        <v>0.5091</v>
       </c>
       <c r="T23" t="n">
         <v>0.4955</v>
       </c>
       <c r="U23" t="n">
-        <v>0.058</v>
+        <v>0.0136</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8599</v>
+        <v>-1.7591</v>
       </c>
       <c r="E24" t="n">
         <v>-0.7447</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1152</v>
+        <v>-1.0144</v>
       </c>
       <c r="G24" t="n">
         <v>0.2814</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2324</v>
+        <v>0.3332</v>
       </c>
       <c r="T24" t="n">
         <v>0.1652</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V24" t="n">
         <v>-1.214</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6009</v>
+        <v>-1.9775</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.649</v>
+        <v>-2.0593</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0481</v>
+        <v>0.0818</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1594</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4415</v>
+        <v>0.1819</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0905</v>
+        <v>0.6803</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.532</v>
+        <v>-0.4984</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4751</v>
+        <v>-6.1885</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.261</v>
+        <v>-4.9072</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2141</v>
+        <v>-1.2813</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3348</v>
@@ -2482,13 +2482,13 @@
         <v>0.9278</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.23</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1336</v>
+        <v>0.2203</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3831</v>
+        <v>-0.4503</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.223499999999998</v>
+        <v>9.009700000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>10.1559</v>
+        <v>10.1556</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9324</v>
+        <v>-1.1459</v>
       </c>
       <c r="G27" t="n">
         <v>12.1871</v>
@@ -2551,7 +2551,7 @@
         <v>4.4178</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4793</v>
+        <v>-3.479299999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-19.7161</v>
@@ -2560,16 +2560,16 @@
         <v>16.2368</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7325</v>
+        <v>3.5187</v>
       </c>
       <c r="T27" t="n">
-        <v>5.407699999999998</v>
+        <v>5.407799999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.6754</v>
+        <v>-1.8891</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.216600000000001</v>
+        <v>-3.2166</v>
       </c>
       <c r="W27" t="n">
         <v>6.1807</v>
